--- a/evt004_av_vendors_verified.xlsx
+++ b/evt004_av_vendors_verified.xlsx
@@ -611,10 +611,26 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Email Sent</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>00:23 PST</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>19c3210cd826858d</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Nationwide AV company, SF office, 24/7 support</t>
@@ -672,10 +688,26 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Email Sent</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>00:24 PST</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>19c3210fa442b148</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>SF-based, Santa Clara office, corporate events</t>
@@ -733,10 +765,26 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Email Sent</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>00:24 PST</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>19c32112fee4bcbe</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Bay Area full-service, staging/lighting/sound</t>
@@ -794,10 +842,26 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Email Sent</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>00:24 PST</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>19c3211321b9bbe0</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>LA-based, serves SF Bay Area, full production</t>
@@ -855,10 +919,26 @@
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Email Sent</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>00:24 PST</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>19c321152ebfadf2</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Bay Area AV, live events, Silicon Valley</t>
